--- a/items_list.xlsx
+++ b/items_list.xlsx
@@ -1,45 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Uni\Info\1. Semester\EiP\Praktikum\backpackGame\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0AC3E4A-6ACE-4702-AF67-0E0D6DB3C817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{94C2F695-BB30-4CAF-BE6C-B353002778EE}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Tabelle1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+  <si>
+    <t>item_id</t>
+  </si>
+  <si>
+    <t>sprite_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
   <si>
     <t>space_x</t>
   </si>
@@ -47,68 +28,56 @@
     <t>space_y</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>itemID</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>armor</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
     <t>rarity</t>
   </si>
   <si>
-    <t>cost</t>
-  </si>
-  <si>
-    <t>attack</t>
-  </si>
-  <si>
-    <t>armor</t>
-  </si>
-  <si>
     <t>Holzschwert</t>
   </si>
   <si>
+    <t>Waffe</t>
+  </si>
+  <si>
+    <t>common</t>
+  </si>
+  <si>
     <t>Holzschild</t>
   </si>
   <si>
+    <t>Rüstung</t>
+  </si>
+  <si>
     <t>Brustpanzer</t>
   </si>
   <si>
+    <t>uncommon</t>
+  </si>
+  <si>
     <t>Stein</t>
-  </si>
-  <si>
-    <t>Waffe</t>
-  </si>
-  <si>
-    <t>Rüstung</t>
-  </si>
-  <si>
-    <t>common</t>
-  </si>
-  <si>
-    <t>uncommon</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -135,7 +104,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -150,26 +119,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A1845CA9-BE1E-43F0-B0F3-38D2C24AB734}" name="Tabelle1" displayName="Tabelle1" ref="A1:I19" totalsRowShown="0">
-  <autoFilter ref="A1:I19" xr:uid="{A1845CA9-BE1E-43F0-B0F3-38D2C24AB734}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{23571407-7E52-404C-B171-4DE9C53ACFA1}" name="itemID"/>
-    <tableColumn id="2" xr3:uid="{A4C26F96-89F8-4BBC-A959-02A51210C96F}" name="name"/>
-    <tableColumn id="3" xr3:uid="{965D2E91-84C2-40EB-89BC-D3C79AF9BBE3}" name="space_x"/>
-    <tableColumn id="4" xr3:uid="{DC3544B8-44B3-4B9D-8635-15EB994AFE47}" name="space_y"/>
-    <tableColumn id="5" xr3:uid="{3D5CA483-D601-4991-8BAA-B550065BECFF}" name="type"/>
-    <tableColumn id="6" xr3:uid="{7B490FD3-3168-4F74-AD77-9B8E22DC8A82}" name="attack"/>
-    <tableColumn id="7" xr3:uid="{36670E0E-7EF6-4E71-A5BC-9719B543EC1C}" name="armor"/>
-    <tableColumn id="8" xr3:uid="{55B8FBC9-1A29-48FA-896C-8A234048CAB9}" name="cost"/>
-    <tableColumn id="10" xr3:uid="{259DD389-BB6B-4E09-A0B1-06E04C0906F6}" name="rarity"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -179,44 +130,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -244,31 +195,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -296,23 +230,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -324,136 +241,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -475,169 +436,179 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5D3397-E8EE-4798-B6AB-26C050834E89}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="25" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
       <c r="D1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>5</v>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
       <c r="H3">
         <v>3</v>
       </c>
-      <c r="I3" t="s">
-        <v>15</v>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
+      <c r="B4">
         <v>2</v>
       </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
       <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
       </c>
       <c r="H4">
         <v>5</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
         <v>12</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/items_list.xlsx
+++ b/items_list.xlsx
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -541,10 +541,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -784,13 +784,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -866,13 +866,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -910,10 +910,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -951,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -992,10 +992,10 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1484,10 +1484,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1604,13 +1604,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1768,13 +1768,13 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1973,13 +1973,13 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>4</v>
       </c>
       <c r="I41" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I43" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2506,13 +2506,13 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H56" t="n">
         <v>5</v>
       </c>
       <c r="I56" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2755,10 +2755,10 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I57" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2793,13 +2793,13 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2834,13 +2834,13 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
